--- a/AAII_Financials/Yearly/WOWI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WOWI_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
   <si>
     <t>WOWI</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -699,8 +699,8 @@
       <c r="I7" s="2">
         <v>39082</v>
       </c>
-      <c r="J7" s="2">
-        <v>38717</v>
+      <c r="J7" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -729,8 +729,8 @@
       <c r="I8" s="3">
         <v>30300</v>
       </c>
-      <c r="J8" s="3">
-        <v>77800</v>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -759,8 +759,8 @@
       <c r="I9" s="3">
         <v>19100</v>
       </c>
-      <c r="J9" s="3">
-        <v>59200</v>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -789,8 +789,8 @@
       <c r="I10" s="3">
         <v>11300</v>
       </c>
-      <c r="J10" s="3">
-        <v>18600</v>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -893,8 +893,8 @@
       <c r="I14" s="3">
         <v>6600</v>
       </c>
-      <c r="J14" s="3">
-        <v>6800</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -923,8 +923,8 @@
       <c r="I15" s="3">
         <v>3700</v>
       </c>
-      <c r="J15" s="3">
-        <v>6100</v>
+      <c r="J15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -964,8 +964,8 @@
       <c r="I17" s="3">
         <v>50100</v>
       </c>
-      <c r="J17" s="3">
-        <v>118000</v>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -994,8 +994,8 @@
       <c r="I18" s="3">
         <v>-19800</v>
       </c>
-      <c r="J18" s="3">
-        <v>-40200</v>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1038,8 +1038,8 @@
       <c r="I20" s="3">
         <v>600</v>
       </c>
-      <c r="J20" s="3">
-        <v>1000</v>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1068,8 +1068,8 @@
       <c r="I21" s="3">
         <v>-15400</v>
       </c>
-      <c r="J21" s="3">
-        <v>-33100</v>
+      <c r="J21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1128,8 +1128,8 @@
       <c r="I23" s="3">
         <v>-19200</v>
       </c>
-      <c r="J23" s="3">
-        <v>-39200</v>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1158,8 +1158,8 @@
       <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>500</v>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1218,8 +1218,8 @@
       <c r="I26" s="3">
         <v>-19200</v>
       </c>
-      <c r="J26" s="3">
-        <v>-39800</v>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1248,8 +1248,8 @@
       <c r="I27" s="3">
         <v>-19200</v>
       </c>
-      <c r="J27" s="3">
-        <v>-39800</v>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1398,8 +1398,8 @@
       <c r="I32" s="3">
         <v>-600</v>
       </c>
-      <c r="J32" s="3">
-        <v>-1000</v>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1428,8 +1428,8 @@
       <c r="I33" s="3">
         <v>-19200</v>
       </c>
-      <c r="J33" s="3">
-        <v>-39800</v>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1488,8 +1488,8 @@
       <c r="I35" s="3">
         <v>-19200</v>
       </c>
-      <c r="J35" s="3">
-        <v>-39800</v>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1523,8 +1523,8 @@
       <c r="I38" s="2">
         <v>39082</v>
       </c>
-      <c r="J38" s="2">
-        <v>38717</v>
+      <c r="J38" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1581,8 +1581,8 @@
       <c r="I41" s="3">
         <v>12000</v>
       </c>
-      <c r="J41" s="3">
-        <v>17800</v>
+      <c r="J41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1641,8 +1641,8 @@
       <c r="I43" s="3">
         <v>2200</v>
       </c>
-      <c r="J43" s="3">
-        <v>12000</v>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1701,8 +1701,8 @@
       <c r="I45" s="3">
         <v>5700</v>
       </c>
-      <c r="J45" s="3">
-        <v>8600</v>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -1731,8 +1731,8 @@
       <c r="I46" s="3">
         <v>19800</v>
       </c>
-      <c r="J46" s="3">
-        <v>38400</v>
+      <c r="J46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1791,8 +1791,8 @@
       <c r="I48" s="3">
         <v>3000</v>
       </c>
-      <c r="J48" s="3">
-        <v>8000</v>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -1821,8 +1821,8 @@
       <c r="I49" s="3">
         <v>4700</v>
       </c>
-      <c r="J49" s="3">
-        <v>5400</v>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -1911,8 +1911,8 @@
       <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3">
-        <v>300</v>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -1971,8 +1971,8 @@
       <c r="I54" s="3">
         <v>27600</v>
       </c>
-      <c r="J54" s="3">
-        <v>52000</v>
+      <c r="J54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2029,8 +2029,8 @@
       <c r="I57" s="3">
         <v>1000</v>
       </c>
-      <c r="J57" s="3">
-        <v>500</v>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2089,8 +2089,8 @@
       <c r="I59" s="3">
         <v>5600</v>
       </c>
-      <c r="J59" s="3">
-        <v>11200</v>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2119,8 +2119,8 @@
       <c r="I60" s="3">
         <v>6600</v>
       </c>
-      <c r="J60" s="3">
-        <v>11700</v>
+      <c r="J60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2179,8 +2179,8 @@
       <c r="I62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3">
-        <v>600</v>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2299,8 +2299,8 @@
       <c r="I66" s="3">
         <v>7000</v>
       </c>
-      <c r="J66" s="3">
-        <v>12300</v>
+      <c r="J66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2463,8 +2463,8 @@
       <c r="I72" s="3">
         <v>-99500</v>
       </c>
-      <c r="J72" s="3">
-        <v>-80300</v>
+      <c r="J72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2583,8 +2583,8 @@
       <c r="I76" s="3">
         <v>20600</v>
       </c>
-      <c r="J76" s="3">
-        <v>39700</v>
+      <c r="J76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2648,8 +2648,8 @@
       <c r="I80" s="2">
         <v>39082</v>
       </c>
-      <c r="J80" s="2">
-        <v>38717</v>
+      <c r="J80" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -2678,8 +2678,8 @@
       <c r="I81" s="3">
         <v>-19200</v>
       </c>
-      <c r="J81" s="3">
-        <v>-39800</v>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -2722,8 +2722,8 @@
       <c r="I83" s="3">
         <v>3700</v>
       </c>
-      <c r="J83" s="3">
-        <v>6100</v>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -2902,8 +2902,8 @@
       <c r="I89" s="3">
         <v>-8600</v>
       </c>
-      <c r="J89" s="3">
-        <v>-28300</v>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -2946,8 +2946,8 @@
       <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>-1700</v>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3036,8 +3036,8 @@
       <c r="I94" s="3">
         <v>2800</v>
       </c>
-      <c r="J94" s="3">
-        <v>22000</v>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3200,8 +3200,8 @@
       <c r="I100" s="3">
         <v>0</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3260,8 +3260,8 @@
       <c r="I102" s="3">
         <v>-5800</v>
       </c>
-      <c r="J102" s="3">
-        <v>-6300</v>
+      <c r="J102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
